--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -3706,10 +3706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118587849</v>
+        <v>118587106</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>96807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3718,50 +3718,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fläcksberget V (Fläcksberget V), Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467399</v>
+        <v>467580</v>
       </c>
       <c r="R30" t="n">
-        <v>6875367</v>
+        <v>6875466</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ett blommande exemplar.</t>
+          <t>Oräkneligt antal, fler än 300.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3822,7 +3813,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118587643</v>
+        <v>118587849</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3857,7 +3848,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3871,10 +3862,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467611</v>
+        <v>467399</v>
       </c>
       <c r="R31" t="n">
-        <v>6875400</v>
+        <v>6875367</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3911,7 +3902,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fyra blommande exemplar.</t>
+          <t>Ett blommande exemplar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,10 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118587106</v>
+        <v>118587643</v>
       </c>
       <c r="B32" t="n">
-        <v>96807</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3950,41 +3941,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fläcksberget V (Fläcksberget V), Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467580</v>
+        <v>467611</v>
       </c>
       <c r="R32" t="n">
-        <v>6875466</v>
+        <v>6875400</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Oräkneligt antal, fler än 300.</t>
+          <t>Fyra blommande exemplar.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -3706,10 +3706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118587106</v>
+        <v>118587849</v>
       </c>
       <c r="B30" t="n">
-        <v>96807</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3718,41 +3718,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fläcksberget V (Fläcksberget V), Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467580</v>
+        <v>467399</v>
       </c>
       <c r="R30" t="n">
-        <v>6875466</v>
+        <v>6875367</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3776,17 +3785,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Oräkneligt antal, fler än 300.</t>
+          <t>Ett blommande exemplar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,7 +3822,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118587849</v>
+        <v>118587643</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3848,7 +3857,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3862,10 +3871,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467399</v>
+        <v>467611</v>
       </c>
       <c r="R31" t="n">
-        <v>6875367</v>
+        <v>6875400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3902,7 +3911,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ett blommande exemplar.</t>
+          <t>Fyra blommande exemplar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118587643</v>
+        <v>118587106</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>96807</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3941,50 +3950,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fläcksberget V (Fläcksberget V), Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467611</v>
+        <v>467580</v>
       </c>
       <c r="R32" t="n">
-        <v>6875400</v>
+        <v>6875466</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Fyra blommande exemplar.</t>
+          <t>Oräkneligt antal, fler än 300.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -3709,7 +3709,7 @@
         <v>118587849</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>118587643</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>118587106</v>
       </c>
       <c r="B32" t="n">
-        <v>96807</v>
+        <v>96814</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -3706,10 +3706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118587849</v>
+        <v>118587106</v>
       </c>
       <c r="B30" t="n">
-        <v>97853</v>
+        <v>96814</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3718,50 +3718,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fläcksberget V (Fläcksberget V), Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467399</v>
+        <v>467580</v>
       </c>
       <c r="R30" t="n">
-        <v>6875367</v>
+        <v>6875466</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ett blommande exemplar.</t>
+          <t>Oräkneligt antal, fler än 300.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,10 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118587106</v>
+        <v>118587849</v>
       </c>
       <c r="B32" t="n">
-        <v>96814</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3950,41 +3941,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fläcksberget V (Fläcksberget V), Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467580</v>
+        <v>467399</v>
       </c>
       <c r="R32" t="n">
-        <v>6875466</v>
+        <v>6875367</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Oräkneligt antal, fler än 300.</t>
+          <t>Ett blommande exemplar.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4402,6 +4402,243 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120101759</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467781</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6875230</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120101688</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>467781</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6875230</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4045,10 +4045,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119705999</v>
+        <v>119706366</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4057,52 +4057,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467790</v>
+        <v>467673</v>
       </c>
       <c r="R33" t="n">
-        <v>6875238</v>
+        <v>6875271</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4134,7 +4120,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4144,7 +4130,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4171,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119706366</v>
+        <v>119705999</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4183,38 +4169,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467673</v>
+        <v>467790</v>
       </c>
       <c r="R34" t="n">
-        <v>6875271</v>
+        <v>6875238</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4404,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120101759</v>
+        <v>120101688</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>56522</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,35 +4416,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4489,11 +4499,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4520,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120101688</v>
+        <v>120101759</v>
       </c>
       <c r="B37" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4532,45 +4537,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4615,6 +4610,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4045,10 +4045,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119706366</v>
+        <v>119706277</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4057,28 +4057,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
@@ -4120,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4130,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4283,10 +4292,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119706277</v>
+        <v>119706366</v>
       </c>
       <c r="B35" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4295,37 +4304,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4639,6 +4639,752 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120182061</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78171</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>467868</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6875214</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120176783</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>467915</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6875340</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120177573</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>467874</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6875439</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120178153</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>467623</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6875374</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120176592</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78262</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>467835</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6875180</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120178856</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78262</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>467636</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6875381</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120178180</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>467592</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6875379</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4854,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120177573</v>
+        <v>120178153</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4866,47 +4866,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467874</v>
+        <v>467623</v>
       </c>
       <c r="R40" t="n">
-        <v>6875439</v>
+        <v>6875374</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4939,11 +4930,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4970,10 +4956,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120178153</v>
+        <v>120177573</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4982,38 +4968,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467623</v>
+        <v>467874</v>
       </c>
       <c r="R41" t="n">
-        <v>6875374</v>
+        <v>6875439</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5046,6 +5041,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4045,10 +4045,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119706277</v>
+        <v>119705999</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4085,7 +4085,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4094,10 +4099,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467673</v>
+        <v>467790</v>
       </c>
       <c r="R33" t="n">
-        <v>6875271</v>
+        <v>6875238</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4129,7 +4134,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4144,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4166,10 +4171,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119705999</v>
+        <v>119706277</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4182,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4206,12 +4211,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467790</v>
+        <v>467673</v>
       </c>
       <c r="R34" t="n">
-        <v>6875238</v>
+        <v>6875271</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120182061</v>
+        <v>120178856</v>
       </c>
       <c r="B38" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4681,13 +4681,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467868</v>
+        <v>467636</v>
       </c>
       <c r="R38" t="n">
-        <v>6875214</v>
+        <v>6875381</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120176783</v>
+        <v>120176592</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4755,47 +4755,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467915</v>
+        <v>467835</v>
       </c>
       <c r="R39" t="n">
-        <v>6875340</v>
+        <v>6875180</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5072,10 +5063,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120176592</v>
+        <v>120182061</v>
       </c>
       <c r="B42" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5088,21 +5079,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5112,13 +5103,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467835</v>
+        <v>467868</v>
       </c>
       <c r="R42" t="n">
-        <v>6875180</v>
+        <v>6875214</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5174,10 +5165,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120178856</v>
+        <v>120176783</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5186,38 +5177,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467636</v>
+        <v>467915</v>
       </c>
       <c r="R43" t="n">
-        <v>6875381</v>
+        <v>6875340</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4407,7 +4407,7 @@
         <v>120101688</v>
       </c>
       <c r="B36" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>120101759</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120178856</v>
+        <v>120176783</v>
       </c>
       <c r="B38" t="n">
-        <v>78262</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4653,38 +4653,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467636</v>
+        <v>467915</v>
       </c>
       <c r="R38" t="n">
-        <v>6875381</v>
+        <v>6875340</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4743,10 +4752,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120176592</v>
+        <v>120182061</v>
       </c>
       <c r="B39" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4759,21 +4768,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4783,13 +4792,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467835</v>
+        <v>467868</v>
       </c>
       <c r="R39" t="n">
-        <v>6875180</v>
+        <v>6875214</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4845,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120178153</v>
+        <v>120178180</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>56532</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4861,34 +4870,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467623</v>
+        <v>467592</v>
       </c>
       <c r="R40" t="n">
-        <v>6875374</v>
+        <v>6875379</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4950,7 +4968,7 @@
         <v>120177573</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5063,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120182061</v>
+        <v>120176592</v>
       </c>
       <c r="B42" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5079,21 +5097,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5103,13 +5121,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467868</v>
+        <v>467835</v>
       </c>
       <c r="R42" t="n">
-        <v>6875214</v>
+        <v>6875180</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5165,10 +5183,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120176783</v>
+        <v>120178153</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,26 +5216,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467915</v>
+        <v>467623</v>
       </c>
       <c r="R43" t="n">
-        <v>6875340</v>
+        <v>6875374</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5276,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120178180</v>
+        <v>120178856</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5288,47 +5297,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467592</v>
+        <v>467636</v>
       </c>
       <c r="R44" t="n">
-        <v>6875379</v>
+        <v>6875381</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4404,10 +4404,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120101688</v>
+        <v>120101759</v>
       </c>
       <c r="B36" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,45 +4416,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4499,6 +4489,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,10 +4520,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120101759</v>
+        <v>120101688</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4537,35 +4532,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4610,11 +4615,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4641,7 +4641,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120176783</v>
+        <v>120178153</v>
       </c>
       <c r="B38" t="n">
         <v>91858</v>
@@ -4674,26 +4674,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467915</v>
+        <v>467623</v>
       </c>
       <c r="R38" t="n">
-        <v>6875340</v>
+        <v>6875374</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4752,10 +4743,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120182061</v>
+        <v>120176783</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4764,41 +4755,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467868</v>
+        <v>467915</v>
       </c>
       <c r="R39" t="n">
-        <v>6875214</v>
+        <v>6875340</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120178180</v>
+        <v>120177573</v>
       </c>
       <c r="B40" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4866,35 +4866,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467592</v>
+        <v>467874</v>
       </c>
       <c r="R40" t="n">
-        <v>6875379</v>
+        <v>6875439</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4939,6 +4939,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,10 +4970,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120177573</v>
+        <v>120178856</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4977,47 +4982,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467874</v>
+        <v>467636</v>
       </c>
       <c r="R41" t="n">
-        <v>6875439</v>
+        <v>6875381</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5050,11 +5046,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120176592</v>
+        <v>120178180</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5093,38 +5084,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467835</v>
+        <v>467592</v>
       </c>
       <c r="R42" t="n">
-        <v>6875180</v>
+        <v>6875379</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120178153</v>
+        <v>120176592</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5195,25 +5195,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467623</v>
+        <v>467835</v>
       </c>
       <c r="R43" t="n">
-        <v>6875374</v>
+        <v>6875180</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5285,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120178856</v>
+        <v>120182061</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467636</v>
+        <v>467868</v>
       </c>
       <c r="R44" t="n">
-        <v>6875381</v>
+        <v>6875214</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120178153</v>
+        <v>120177573</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4653,38 +4653,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467623</v>
+        <v>467874</v>
       </c>
       <c r="R38" t="n">
-        <v>6875374</v>
+        <v>6875439</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4717,6 +4726,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4743,7 +4757,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120176783</v>
+        <v>120178153</v>
       </c>
       <c r="B39" t="n">
         <v>91858</v>
@@ -4776,26 +4790,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467915</v>
+        <v>467623</v>
       </c>
       <c r="R39" t="n">
-        <v>6875340</v>
+        <v>6875374</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4854,10 +4859,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120177573</v>
+        <v>120176783</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4866,35 +4871,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467874</v>
+        <v>467915</v>
       </c>
       <c r="R40" t="n">
-        <v>6875439</v>
+        <v>6875340</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4939,11 +4944,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4404,10 +4404,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120101759</v>
+        <v>120101688</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,35 +4416,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4489,11 +4499,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4520,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120101688</v>
+        <v>120101759</v>
       </c>
       <c r="B37" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4532,45 +4537,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4615,6 +4610,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120177573</v>
+        <v>120178153</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4653,47 +4653,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467874</v>
+        <v>467623</v>
       </c>
       <c r="R38" t="n">
-        <v>6875439</v>
+        <v>6875374</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4726,11 +4717,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4757,10 +4743,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120178153</v>
+        <v>120178180</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>56532</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4773,34 +4759,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467623</v>
+        <v>467592</v>
       </c>
       <c r="R39" t="n">
-        <v>6875374</v>
+        <v>6875379</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4859,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120176783</v>
+        <v>120176592</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4871,47 +4866,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467915</v>
+        <v>467835</v>
       </c>
       <c r="R40" t="n">
-        <v>6875340</v>
+        <v>6875180</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4970,10 +4956,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120178856</v>
+        <v>120182061</v>
       </c>
       <c r="B41" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4986,21 +4972,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5010,13 +4996,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467636</v>
+        <v>467868</v>
       </c>
       <c r="R41" t="n">
-        <v>6875381</v>
+        <v>6875214</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5072,10 +5058,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120178180</v>
+        <v>120177573</v>
       </c>
       <c r="B42" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5084,35 +5070,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5121,10 +5107,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467592</v>
+        <v>467874</v>
       </c>
       <c r="R42" t="n">
-        <v>6875379</v>
+        <v>6875439</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5157,6 +5143,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5183,7 +5174,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120176592</v>
+        <v>120178856</v>
       </c>
       <c r="B43" t="n">
         <v>78278</v>
@@ -5223,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467835</v>
+        <v>467636</v>
       </c>
       <c r="R43" t="n">
-        <v>6875180</v>
+        <v>6875381</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5285,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120182061</v>
+        <v>120176783</v>
       </c>
       <c r="B44" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5297,41 +5288,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467868</v>
+        <v>467915</v>
       </c>
       <c r="R44" t="n">
-        <v>6875214</v>
+        <v>6875340</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4404,10 +4404,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120101688</v>
+        <v>120101759</v>
       </c>
       <c r="B36" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,45 +4416,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4499,6 +4489,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,10 +4520,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120101759</v>
+        <v>120101688</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4537,35 +4532,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4610,11 +4615,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120178153</v>
+        <v>120178180</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>56532</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4657,34 +4657,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467623</v>
+        <v>467592</v>
       </c>
       <c r="R38" t="n">
-        <v>6875374</v>
+        <v>6875379</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4743,10 +4752,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120178180</v>
+        <v>120177573</v>
       </c>
       <c r="B39" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4755,35 +4764,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4792,10 +4801,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467592</v>
+        <v>467874</v>
       </c>
       <c r="R39" t="n">
-        <v>6875379</v>
+        <v>6875439</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4828,6 +4837,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4854,7 +4868,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120176592</v>
+        <v>120178856</v>
       </c>
       <c r="B40" t="n">
         <v>78278</v>
@@ -4894,10 +4908,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467835</v>
+        <v>467636</v>
       </c>
       <c r="R40" t="n">
-        <v>6875180</v>
+        <v>6875381</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4956,10 +4970,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120182061</v>
+        <v>120176783</v>
       </c>
       <c r="B41" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4968,41 +4982,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467868</v>
+        <v>467915</v>
       </c>
       <c r="R41" t="n">
-        <v>6875214</v>
+        <v>6875340</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120177573</v>
+        <v>120178153</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5070,47 +5093,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467874</v>
+        <v>467623</v>
       </c>
       <c r="R42" t="n">
-        <v>6875439</v>
+        <v>6875374</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5143,11 +5157,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5174,7 +5183,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120178856</v>
+        <v>120176592</v>
       </c>
       <c r="B43" t="n">
         <v>78278</v>
@@ -5214,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467636</v>
+        <v>467835</v>
       </c>
       <c r="R43" t="n">
-        <v>6875381</v>
+        <v>6875180</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5276,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120176783</v>
+        <v>120182061</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5288,50 +5297,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467915</v>
+        <v>467868</v>
       </c>
       <c r="R44" t="n">
-        <v>6875340</v>
+        <v>6875214</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120178180</v>
+        <v>120178153</v>
       </c>
       <c r="B38" t="n">
-        <v>56532</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4657,43 +4657,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467592</v>
+        <v>467623</v>
       </c>
       <c r="R38" t="n">
-        <v>6875379</v>
+        <v>6875374</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4752,10 +4743,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120177573</v>
+        <v>120178180</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4764,35 +4755,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4801,10 +4792,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467874</v>
+        <v>467592</v>
       </c>
       <c r="R39" t="n">
-        <v>6875439</v>
+        <v>6875379</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4837,11 +4828,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4868,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120178856</v>
+        <v>120182061</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4884,21 +4870,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4908,13 +4894,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467636</v>
+        <v>467868</v>
       </c>
       <c r="R40" t="n">
-        <v>6875381</v>
+        <v>6875214</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4970,10 +4956,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120176783</v>
+        <v>120178856</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4982,47 +4968,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467915</v>
+        <v>467636</v>
       </c>
       <c r="R41" t="n">
-        <v>6875340</v>
+        <v>6875381</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5081,10 +5058,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120178153</v>
+        <v>120177573</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5093,38 +5070,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467623</v>
+        <v>467874</v>
       </c>
       <c r="R42" t="n">
-        <v>6875374</v>
+        <v>6875439</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5157,6 +5143,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5285,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120182061</v>
+        <v>120176783</v>
       </c>
       <c r="B44" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5297,41 +5288,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467868</v>
+        <v>467915</v>
       </c>
       <c r="R44" t="n">
-        <v>6875214</v>
+        <v>6875340</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4641,10 +4641,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120178153</v>
+        <v>120182061</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4653,25 +4653,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4681,13 +4681,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467623</v>
+        <v>467868</v>
       </c>
       <c r="R38" t="n">
-        <v>6875374</v>
+        <v>6875214</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120178180</v>
+        <v>120176783</v>
       </c>
       <c r="B39" t="n">
-        <v>56532</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4781,9 +4781,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467592</v>
+        <v>467915</v>
       </c>
       <c r="R39" t="n">
-        <v>6875379</v>
+        <v>6875340</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120182061</v>
+        <v>120176592</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4870,21 +4870,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4894,13 +4894,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467868</v>
+        <v>467835</v>
       </c>
       <c r="R40" t="n">
-        <v>6875214</v>
+        <v>6875180</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5058,10 +5058,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120177573</v>
+        <v>120178153</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5070,47 +5070,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467874</v>
+        <v>467623</v>
       </c>
       <c r="R42" t="n">
-        <v>6875439</v>
+        <v>6875374</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5143,11 +5134,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5174,10 +5160,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120176592</v>
+        <v>120178180</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5186,38 +5172,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467835</v>
+        <v>467592</v>
       </c>
       <c r="R43" t="n">
-        <v>6875180</v>
+        <v>6875379</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120176783</v>
+        <v>120177573</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5288,35 +5283,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467915</v>
+        <v>467874</v>
       </c>
       <c r="R44" t="n">
-        <v>6875340</v>
+        <v>6875439</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5361,6 +5356,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -4404,10 +4404,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120101759</v>
+        <v>120101688</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,35 +4416,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4489,11 +4499,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4520,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120101688</v>
+        <v>120101759</v>
       </c>
       <c r="B37" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4532,45 +4537,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4615,6 +4610,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4743,10 +4743,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120176783</v>
+        <v>120178856</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4755,47 +4755,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467915</v>
+        <v>467636</v>
       </c>
       <c r="R39" t="n">
-        <v>6875340</v>
+        <v>6875381</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4854,10 +4845,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120176592</v>
+        <v>120178153</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4866,25 +4857,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4894,10 +4885,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467835</v>
+        <v>467623</v>
       </c>
       <c r="R40" t="n">
-        <v>6875180</v>
+        <v>6875374</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4956,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120178856</v>
+        <v>120176783</v>
       </c>
       <c r="B41" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4968,38 +4959,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467636</v>
+        <v>467915</v>
       </c>
       <c r="R41" t="n">
-        <v>6875381</v>
+        <v>6875340</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5058,10 +5058,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120178153</v>
+        <v>120178180</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>56532</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5074,34 +5074,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467623</v>
+        <v>467592</v>
       </c>
       <c r="R42" t="n">
-        <v>6875374</v>
+        <v>6875379</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5160,10 +5169,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120178180</v>
+        <v>120177573</v>
       </c>
       <c r="B43" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5172,35 +5181,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5209,10 +5218,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467592</v>
+        <v>467874</v>
       </c>
       <c r="R43" t="n">
-        <v>6875379</v>
+        <v>6875439</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5245,6 +5254,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5271,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120177573</v>
+        <v>120176592</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5283,47 +5297,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467874</v>
+        <v>467835</v>
       </c>
       <c r="R44" t="n">
-        <v>6875439</v>
+        <v>6875180</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5356,11 +5361,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101933482</v>
+        <v>120182061</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467592.6242949227</v>
+        <v>467868</v>
       </c>
       <c r="R2" t="n">
-        <v>6875417.562916294</v>
+        <v>6875214</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101933453</v>
+        <v>111908700</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,39 +783,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467583.4410242627</v>
+        <v>467922</v>
       </c>
       <c r="R3" t="n">
-        <v>6875342.498744056</v>
+        <v>6875306</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Förekomst av doftticka i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,55 +884,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101933379</v>
+        <v>111942953</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467433.3045680952</v>
+        <v>468248</v>
       </c>
       <c r="R4" t="n">
-        <v>6875383.38952559</v>
+        <v>6875167</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,22 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,15 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101933494</v>
+        <v>112014229</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,39 +993,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467613.6914534386</v>
+        <v>467427</v>
       </c>
       <c r="R5" t="n">
-        <v>6875407.028746434</v>
+        <v>6875290</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,54 +1080,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104939578</v>
+        <v>111911493</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Gröbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467787.7758703761</v>
+        <v>467728</v>
       </c>
       <c r="R6" t="n">
-        <v>6875460.797173257</v>
+        <v>6874766</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,37 +1178,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104939556</v>
+        <v>111909766</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,13 +1214,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467814.8803209669</v>
+        <v>467757</v>
       </c>
       <c r="R7" t="n">
-        <v>6875541.325464724</v>
+        <v>6875470</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1244,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,54 +1276,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104939568</v>
+        <v>112014208</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467821.1535541386</v>
+        <v>467418</v>
       </c>
       <c r="R8" t="n">
-        <v>6875508.388576465</v>
+        <v>6875312</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,22 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,54 +1374,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105096262</v>
+        <v>112014423</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fläcksberget, Sveg, Hjd, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467919.6866759416</v>
+        <v>467430</v>
       </c>
       <c r="R9" t="n">
-        <v>6875083.778890509</v>
+        <v>6875238</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,22 +1440,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,37 +1472,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111527876</v>
+        <v>112014834</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467615.2905344999</v>
+        <v>467492</v>
       </c>
       <c r="R10" t="n">
-        <v>6875426.740629551</v>
+        <v>6875044</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1654,22 +1538,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,51 +1570,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111528980</v>
+        <v>112015011</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467799.8074815667</v>
+        <v>467390</v>
       </c>
       <c r="R11" t="n">
-        <v>6875539.119922069</v>
+        <v>6875328</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1767,22 +1636,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,51 +1668,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111528300</v>
+        <v>111908364</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Gröbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467795.2212022893</v>
+        <v>467724</v>
       </c>
       <c r="R12" t="n">
-        <v>6875452.272210476</v>
+        <v>6874811</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1880,27 +1734,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tre blommande.</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,54 +1766,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111528203</v>
+        <v>105096262</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Sveg, Hjd, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467745.6122397452</v>
+        <v>467919</v>
       </c>
       <c r="R13" t="n">
-        <v>6875429.258361855</v>
+        <v>6875084</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,22 +1832,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,55 +1864,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111908768</v>
+        <v>112014142</v>
       </c>
       <c r="B14" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467912</v>
+        <v>467443</v>
       </c>
       <c r="R14" t="n">
-        <v>6875299</v>
+        <v>6875337</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2115,12 +1930,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,51 +1962,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111909766</v>
+        <v>119706366</v>
       </c>
       <c r="B15" t="n">
-        <v>89331</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467757</v>
+        <v>467673</v>
       </c>
       <c r="R15" t="n">
-        <v>6875470</v>
+        <v>6875271</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2218,12 +2027,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,27 +2057,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111908364</v>
+        <v>120176783</v>
       </c>
       <c r="B16" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,35 +2080,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gröbäcken, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467724</v>
+        <v>467915</v>
       </c>
       <c r="R16" t="n">
-        <v>6874811</v>
+        <v>6875340</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2321,12 +2143,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,60 +2175,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111908700</v>
+        <v>120178153</v>
       </c>
       <c r="B17" t="n">
-        <v>90113</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467922</v>
+        <v>467623</v>
       </c>
       <c r="R17" t="n">
-        <v>6875307</v>
+        <v>6875374</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2433,17 +2240,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Förekomst av doftticka i avverkningsanmält område.</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,15 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111909174</v>
+        <v>112014347</v>
       </c>
       <c r="B18" t="n">
-        <v>77402</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,35 +2283,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467989</v>
+        <v>467430</v>
       </c>
       <c r="R18" t="n">
-        <v>6875353</v>
+        <v>6875238</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2541,12 +2338,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,15 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111909536</v>
+        <v>112014177</v>
       </c>
       <c r="B19" t="n">
-        <v>77402</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,35 +2381,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467891</v>
+        <v>467390</v>
       </c>
       <c r="R19" t="n">
-        <v>6875425</v>
+        <v>6875328</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2644,12 +2436,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,15 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111942712</v>
+        <v>112014300</v>
       </c>
       <c r="B20" t="n">
-        <v>77402</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2692,35 +2479,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468231</v>
+        <v>467415</v>
       </c>
       <c r="R20" t="n">
-        <v>6875022</v>
+        <v>6875288</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2747,12 +2534,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,15 +2566,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112015011</v>
+        <v>112014923</v>
       </c>
       <c r="B21" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2577,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2602,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467390</v>
+        <v>467413</v>
       </c>
       <c r="R21" t="n">
-        <v>6875328</v>
+        <v>6875235</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2882,15 +2664,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112014300</v>
+        <v>111909174</v>
       </c>
       <c r="B22" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,35 +2675,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467415</v>
+        <v>467989</v>
       </c>
       <c r="R22" t="n">
-        <v>6875287</v>
+        <v>6875352</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2953,12 +2730,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,15 +2762,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112014423</v>
+        <v>111909536</v>
       </c>
       <c r="B23" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,35 +2773,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467430</v>
+        <v>467891</v>
       </c>
       <c r="R23" t="n">
-        <v>6875238</v>
+        <v>6875425</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3056,12 +2828,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,51 +2860,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112014142</v>
+        <v>111942712</v>
       </c>
       <c r="B24" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467443</v>
+        <v>468231</v>
       </c>
       <c r="R24" t="n">
-        <v>6875337</v>
+        <v>6875022</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3159,12 +2926,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,15 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112014923</v>
+        <v>111942872</v>
       </c>
       <c r="B25" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3207,35 +2969,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467413</v>
+        <v>468260</v>
       </c>
       <c r="R25" t="n">
-        <v>6875234</v>
+        <v>6875164</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3262,12 +3024,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3294,15 +3056,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112014229</v>
+        <v>120176592</v>
       </c>
       <c r="B26" t="n">
-        <v>90831</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,35 +3067,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467427</v>
+        <v>467835</v>
       </c>
       <c r="R26" t="n">
-        <v>6875290</v>
+        <v>6875180</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3365,12 +3121,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,15 +3153,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112014177</v>
+        <v>120178856</v>
       </c>
       <c r="B27" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3413,35 +3164,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467390</v>
+        <v>467636</v>
       </c>
       <c r="R27" t="n">
-        <v>6875328</v>
+        <v>6875381</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3468,12 +3218,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,15 +3250,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112014208</v>
+        <v>119705999</v>
       </c>
       <c r="B28" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,35 +3261,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467418</v>
+        <v>467790</v>
       </c>
       <c r="R28" t="n">
-        <v>6875313</v>
+        <v>6875238</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3571,12 +3329,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,27 +3359,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112014347</v>
+        <v>120101688</v>
       </c>
       <c r="B29" t="n">
-        <v>90827</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,35 +3382,53 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467430</v>
+        <v>467781</v>
       </c>
       <c r="R29" t="n">
-        <v>6875238</v>
+        <v>6875230</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3674,12 +3455,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3706,62 +3487,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118587849</v>
+        <v>120178180</v>
       </c>
       <c r="B30" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fläcksberget V (Fläcksberget V), Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467399</v>
+        <v>467592</v>
       </c>
       <c r="R30" t="n">
-        <v>6875367</v>
+        <v>6875379</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,17 +3561,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ett blommande exemplar.</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3822,62 +3593,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118587643</v>
+        <v>101933361</v>
       </c>
       <c r="B31" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fläcksberget V (Fläcksberget V), Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467611</v>
+        <v>467341</v>
       </c>
       <c r="R31" t="n">
-        <v>6875400</v>
+        <v>6875408</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3901,17 +3660,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fyra blommande exemplar.</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,53 +3692,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118587106</v>
+        <v>101933401</v>
       </c>
       <c r="B32" t="n">
-        <v>96819</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fläcksberget V (Fläcksberget V), Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467580</v>
+        <v>467487</v>
       </c>
       <c r="R32" t="n">
-        <v>6875466</v>
+        <v>6875372</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4008,17 +3759,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Oräkneligt antal, fler än 300.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,67 +3791,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119705999</v>
+        <v>101933424</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467790</v>
+        <v>467573</v>
       </c>
       <c r="R33" t="n">
-        <v>6875238</v>
+        <v>6875315</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4129,22 +3858,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,74 +3878,62 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119706277</v>
+        <v>101933453</v>
       </c>
       <c r="B34" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467673</v>
+        <v>467584</v>
       </c>
       <c r="R34" t="n">
-        <v>6875271</v>
+        <v>6875343</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4250,22 +3957,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:34</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:34</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4280,65 +3977,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119706366</v>
+        <v>101933471</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467673</v>
+        <v>467562</v>
       </c>
       <c r="R35" t="n">
-        <v>6875271</v>
+        <v>6875360</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4362,22 +4056,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,84 +4076,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120101688</v>
+        <v>101933482</v>
       </c>
       <c r="B36" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467781</v>
+        <v>467592</v>
       </c>
       <c r="R36" t="n">
-        <v>6875230</v>
+        <v>6875418</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4493,12 +4155,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,15 +4187,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120101759</v>
+        <v>101933494</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4558,29 +4215,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467781</v>
+        <v>467614</v>
       </c>
       <c r="R37" t="n">
-        <v>6875230</v>
+        <v>6875407</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4604,17 +4254,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4641,53 +4286,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120178856</v>
+        <v>104939556</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467636</v>
+        <v>467815</v>
       </c>
       <c r="R38" t="n">
-        <v>6875381</v>
+        <v>6875541</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4711,12 +4352,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4743,53 +4384,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120182061</v>
+        <v>104939568</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467868</v>
+        <v>467821</v>
       </c>
       <c r="R39" t="n">
-        <v>6875214</v>
+        <v>6875508</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4813,12 +4450,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4845,53 +4482,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120176592</v>
+        <v>104939578</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467835</v>
+        <v>467788</v>
       </c>
       <c r="R40" t="n">
-        <v>6875180</v>
+        <v>6875461</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4915,12 +4548,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4947,15 +4580,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120177573</v>
+        <v>111527806</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4980,26 +4608,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467874</v>
+        <v>467615</v>
       </c>
       <c r="R41" t="n">
-        <v>6875439</v>
+        <v>6875427</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5026,17 +4646,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5063,59 +4678,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120176783</v>
+        <v>111528203</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467915</v>
+        <v>467745</v>
       </c>
       <c r="R42" t="n">
-        <v>6875340</v>
+        <v>6875430</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5142,12 +4744,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5174,59 +4776,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120178180</v>
+        <v>111528300</v>
       </c>
       <c r="B43" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467592</v>
+        <v>467795</v>
       </c>
       <c r="R43" t="n">
-        <v>6875379</v>
+        <v>6875452</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5253,12 +4842,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tre blommande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5285,50 +4879,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120178153</v>
+        <v>111528980</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467623</v>
+        <v>467800</v>
       </c>
       <c r="R44" t="n">
-        <v>6875374</v>
+        <v>6875540</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5355,12 +4945,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5384,6 +4974,1725 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>111908768</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>467912</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6875300</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118153320</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>467531</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6875351</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tre stycken som är i förstadium till blomning.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118153438</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>467534</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6875341</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En blomknopp.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118153540</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>467572</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6875307</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Två blomknopp.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118587202</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>467585</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6875479</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118587288</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>467579</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6875483</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>En blomma.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118587643</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>467611</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6875400</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fyra blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118587687</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>467571</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6875367</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fem blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118587849</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>467399</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6875367</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ett blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120101759</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>467781</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6875230</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120177573</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>467874</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6875439</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127037135</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>467944</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6875455</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>101933379</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>467433</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6875384</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>118587106</v>
+      </c>
+      <c r="B58" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>467580</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6875466</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Oräkneligt antal, fler än 300.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>118153108</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>467495</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6875373</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>111942915</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>468248</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6875167</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111911493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120182061</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908700</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942953</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014229</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111909766</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014208</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014423</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014834</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112015011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105096262</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014142</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119706366</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120178153</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2367,6 +2452,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014347</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2465,6 +2555,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014177</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2563,6 +2658,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014300</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112014923</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111909174</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2857,6 +2967,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111909536</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2955,6 +3070,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942712</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3052,6 +3172,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176592</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120178856</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3270,6 +3400,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119705999</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3386,6 +3521,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101688</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3492,6 +3632,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120178180</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3591,6 +3736,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933361</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3690,6 +3840,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933401</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3789,6 +3944,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933424</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3888,6 +4048,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933453</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3987,6 +4152,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933471</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4086,6 +4256,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933482</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4185,6 +4360,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933494</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4283,6 +4463,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104939556</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4381,6 +4566,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104939568</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4479,6 +4669,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104939578</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4577,6 +4772,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111527806</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4675,6 +4875,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111528203</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4778,6 +4983,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111528300</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4876,6 +5086,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111528980</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4978,6 +5193,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908768</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5089,6 +5309,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118153320</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5200,6 +5425,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118153438</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5311,6 +5541,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118153540</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5422,6 +5657,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587202</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5533,6 +5773,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587288</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5644,6 +5889,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587643</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5755,6 +6005,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587687</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5866,6 +6121,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587849</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5977,6 +6237,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101759</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6088,6 +6353,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120177573</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6199,6 +6469,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127037135</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6298,6 +6573,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933379</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6400,6 +6680,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587106</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6497,6 +6782,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118153108</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6595,6 +6885,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942915</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6693,8 +6988,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120182061</v>
+        <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>78993</v>
+        <v>93345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,37 +897,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467868</v>
+        <v>468058</v>
       </c>
       <c r="R4" t="n">
-        <v>6875214</v>
+        <v>6874703</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,12 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,64 +996,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120182061</t>
+          <t>https://artportalen.se/Sighting/135808070</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111908700</v>
+        <v>120182061</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467922</v>
+        <v>467868</v>
       </c>
       <c r="R5" t="n">
-        <v>6875306</v>
+        <v>6875214</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,17 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förekomst av doftticka i avverkningsanmält område.</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,16 +1098,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111908700</t>
+          <t>https://artportalen.se/Sighting/120182061</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111942953</v>
+        <v>111908700</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,24 +1115,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468248</v>
+        <v>467922</v>
       </c>
       <c r="R6" t="n">
-        <v>6875167</v>
+        <v>6875306</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1171,12 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Förekomst av doftticka i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,13 +1215,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111942953</t>
+          <t>https://artportalen.se/Sighting/111908700</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112014229</v>
+        <v>111942953</v>
       </c>
       <c r="B7" t="n">
         <v>93213</v>
@@ -1240,14 +1253,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467427</v>
+        <v>468248</v>
       </c>
       <c r="R7" t="n">
-        <v>6875290</v>
+        <v>6875167</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,12 +1287,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,52 +1318,52 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014229</t>
+          <t>https://artportalen.se/Sighting/111942953</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111909766</v>
+        <v>112014229</v>
       </c>
       <c r="B8" t="n">
-        <v>91680</v>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467757</v>
+        <v>467427</v>
       </c>
       <c r="R8" t="n">
-        <v>6875470</v>
+        <v>6875290</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1377,12 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,52 +1421,52 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909766</t>
+          <t>https://artportalen.se/Sighting/112014229</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112014208</v>
+        <v>111909766</v>
       </c>
       <c r="B9" t="n">
-        <v>93189</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467418</v>
+        <v>467757</v>
       </c>
       <c r="R9" t="n">
-        <v>6875312</v>
+        <v>6875470</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1480,12 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,13 +1524,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014208</t>
+          <t>https://artportalen.se/Sighting/111909766</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112014423</v>
+        <v>112014208</v>
       </c>
       <c r="B10" t="n">
         <v>93189</v>
@@ -1553,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467430</v>
+        <v>467418</v>
       </c>
       <c r="R10" t="n">
-        <v>6875238</v>
+        <v>6875312</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1614,13 +1627,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014423</t>
+          <t>https://artportalen.se/Sighting/112014208</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112014834</v>
+        <v>112014423</v>
       </c>
       <c r="B11" t="n">
         <v>93189</v>
@@ -1656,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467492</v>
+        <v>467430</v>
       </c>
       <c r="R11" t="n">
-        <v>6875044</v>
+        <v>6875238</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1717,13 +1730,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014834</t>
+          <t>https://artportalen.se/Sighting/112014423</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112015011</v>
+        <v>112014834</v>
       </c>
       <c r="B12" t="n">
         <v>93189</v>
@@ -1759,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467390</v>
+        <v>467492</v>
       </c>
       <c r="R12" t="n">
-        <v>6875328</v>
+        <v>6875044</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1820,16 +1833,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112015011</t>
+          <t>https://artportalen.se/Sighting/112014834</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105096262</v>
+        <v>112015011</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,38 +1850,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fläcksberget, Sveg, Hjd, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467919</v>
+        <v>467390</v>
       </c>
       <c r="R13" t="n">
-        <v>6875084</v>
+        <v>6875328</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,12 +1905,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,13 +1936,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105096262</t>
+          <t>https://artportalen.se/Sighting/112015011</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112014142</v>
+        <v>105096262</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1961,17 +1974,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Sveg, Hjd, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467443</v>
+        <v>467919</v>
       </c>
       <c r="R14" t="n">
-        <v>6875337</v>
+        <v>6875084</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +2008,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,13 +2039,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014142</t>
+          <t>https://artportalen.se/Sighting/105096262</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119706366</v>
+        <v>112014142</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2061,16 +2074,17 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467673</v>
+        <v>467443</v>
       </c>
       <c r="R15" t="n">
-        <v>6875271</v>
+        <v>6875337</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2097,22 +2111,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,24 +2131,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706366</t>
+          <t>https://artportalen.se/Sighting/112014142</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176783</v>
+        <v>119706366</v>
       </c>
       <c r="B16" t="n">
         <v>93197</v>
@@ -2172,26 +2176,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467915</v>
+        <v>467673</v>
       </c>
       <c r="R16" t="n">
-        <v>6875340</v>
+        <v>6875271</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2218,12 +2213,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,24 +2243,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120176783</t>
+          <t>https://artportalen.se/Sighting/119706366</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120178153</v>
+        <v>120176783</v>
       </c>
       <c r="B17" t="n">
         <v>93197</v>
@@ -2283,17 +2288,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467623</v>
+        <v>467915</v>
       </c>
       <c r="R17" t="n">
-        <v>6875374</v>
+        <v>6875340</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2351,16 +2365,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120178153</t>
+          <t>https://artportalen.se/Sighting/120176783</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112014347</v>
+        <v>120178153</v>
       </c>
       <c r="B18" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2368,35 +2382,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467430</v>
+        <v>467623</v>
       </c>
       <c r="R18" t="n">
-        <v>6875238</v>
+        <v>6875374</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2423,12 +2436,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,16 +2467,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014347</t>
+          <t>https://artportalen.se/Sighting/120178153</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112014177</v>
+        <v>112014347</v>
       </c>
       <c r="B19" t="n">
-        <v>93235</v>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,21 +2484,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467390</v>
+        <v>467430</v>
       </c>
       <c r="R19" t="n">
-        <v>6875328</v>
+        <v>6875238</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2557,13 +2570,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014177</t>
+          <t>https://artportalen.se/Sighting/112014347</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112014300</v>
+        <v>112014177</v>
       </c>
       <c r="B20" t="n">
         <v>93235</v>
@@ -2599,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467415</v>
+        <v>467390</v>
       </c>
       <c r="R20" t="n">
-        <v>6875288</v>
+        <v>6875328</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2660,13 +2673,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014300</t>
+          <t>https://artportalen.se/Sighting/112014177</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112014923</v>
+        <v>112014300</v>
       </c>
       <c r="B21" t="n">
         <v>93235</v>
@@ -2702,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467413</v>
+        <v>467415</v>
       </c>
       <c r="R21" t="n">
-        <v>6875235</v>
+        <v>6875288</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2763,16 +2776,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014923</t>
+          <t>https://artportalen.se/Sighting/112014300</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111909174</v>
+        <v>112014923</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,35 +2793,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467989</v>
+        <v>467413</v>
       </c>
       <c r="R22" t="n">
-        <v>6875352</v>
+        <v>6875235</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2835,12 +2848,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2866,13 +2879,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909174</t>
+          <t>https://artportalen.se/Sighting/112014923</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111909536</v>
+        <v>111909174</v>
       </c>
       <c r="B23" t="n">
         <v>79084</v>
@@ -2908,10 +2921,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467891</v>
+        <v>467989</v>
       </c>
       <c r="R23" t="n">
-        <v>6875425</v>
+        <v>6875352</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2969,13 +2982,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909536</t>
+          <t>https://artportalen.se/Sighting/111909174</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111942712</v>
+        <v>111909536</v>
       </c>
       <c r="B24" t="n">
         <v>79084</v>
@@ -3011,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468231</v>
+        <v>467891</v>
       </c>
       <c r="R24" t="n">
-        <v>6875022</v>
+        <v>6875425</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3041,12 +3054,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3072,13 +3085,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111942712</t>
+          <t>https://artportalen.se/Sighting/111909536</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120176592</v>
+        <v>111942712</v>
       </c>
       <c r="B25" t="n">
         <v>79084</v>
@@ -3107,16 +3120,17 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467835</v>
+        <v>468231</v>
       </c>
       <c r="R25" t="n">
-        <v>6875180</v>
+        <v>6875022</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3143,12 +3157,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3174,13 +3188,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120176592</t>
+          <t>https://artportalen.se/Sighting/111942712</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120178856</v>
+        <v>120176592</v>
       </c>
       <c r="B26" t="n">
         <v>79084</v>
@@ -3215,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467636</v>
+        <v>467835</v>
       </c>
       <c r="R26" t="n">
-        <v>6875381</v>
+        <v>6875180</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3276,16 +3290,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120178856</t>
+          <t>https://artportalen.se/Sighting/120176592</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119705999</v>
+        <v>120178856</v>
       </c>
       <c r="B27" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3293,48 +3307,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467790</v>
+        <v>467636</v>
       </c>
       <c r="R27" t="n">
-        <v>6875238</v>
+        <v>6875381</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3361,22 +3361,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,69 +3381,64 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119705999</t>
+          <t>https://artportalen.se/Sighting/120178856</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120101688</v>
+        <v>119705999</v>
       </c>
       <c r="B28" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3462,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467781</v>
+        <v>467790</v>
       </c>
       <c r="R28" t="n">
-        <v>6875230</v>
+        <v>6875238</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3492,12 +3477,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3512,24 +3507,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101688</t>
+          <t>https://artportalen.se/Sighting/119705999</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120178180</v>
+        <v>120101688</v>
       </c>
       <c r="B29" t="n">
         <v>57141</v>
@@ -3559,12 +3554,22 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3573,10 +3578,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467592</v>
+        <v>467781</v>
       </c>
       <c r="R29" t="n">
-        <v>6875379</v>
+        <v>6875230</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3603,12 +3608,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3634,16 +3639,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120178180</t>
+          <t>https://artportalen.se/Sighting/120101688</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101933361</v>
+        <v>120178180</v>
       </c>
       <c r="B30" t="n">
-        <v>99022</v>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,39 +3656,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220093</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467341</v>
+        <v>467592</v>
       </c>
       <c r="R30" t="n">
-        <v>6875408</v>
+        <v>6875379</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3707,12 +3719,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3738,38 +3750,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933361</t>
+          <t>https://artportalen.se/Sighting/120178180</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101933401</v>
+        <v>101933361</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467487</v>
+        <v>467341</v>
       </c>
       <c r="R31" t="n">
-        <v>6875372</v>
+        <v>6875408</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3811,12 +3823,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,13 +3854,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933401</t>
+          <t>https://artportalen.se/Sighting/101933361</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101933424</v>
+        <v>101933401</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -3885,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467573</v>
+        <v>467487</v>
       </c>
       <c r="R32" t="n">
-        <v>6875315</v>
+        <v>6875372</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3946,13 +3958,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933424</t>
+          <t>https://artportalen.se/Sighting/101933401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101933453</v>
+        <v>101933424</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -3989,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467584</v>
+        <v>467573</v>
       </c>
       <c r="R33" t="n">
-        <v>6875343</v>
+        <v>6875315</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4050,13 +4062,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933453</t>
+          <t>https://artportalen.se/Sighting/101933424</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101933471</v>
+        <v>101933453</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4093,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467562</v>
+        <v>467584</v>
       </c>
       <c r="R34" t="n">
-        <v>6875360</v>
+        <v>6875343</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4154,13 +4166,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933471</t>
+          <t>https://artportalen.se/Sighting/101933453</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101933482</v>
+        <v>101933471</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4197,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467592</v>
+        <v>467562</v>
       </c>
       <c r="R35" t="n">
-        <v>6875418</v>
+        <v>6875360</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4258,13 +4270,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933482</t>
+          <t>https://artportalen.se/Sighting/101933471</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101933494</v>
+        <v>101933482</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4301,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467614</v>
+        <v>467592</v>
       </c>
       <c r="R36" t="n">
-        <v>6875407</v>
+        <v>6875418</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4362,13 +4374,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933494</t>
+          <t>https://artportalen.se/Sighting/101933482</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104939556</v>
+        <v>101933494</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4398,16 +4410,17 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467815</v>
+        <v>467614</v>
       </c>
       <c r="R37" t="n">
-        <v>6875541</v>
+        <v>6875407</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4434,12 +4447,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4465,13 +4478,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104939556</t>
+          <t>https://artportalen.se/Sighting/101933494</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104939568</v>
+        <v>104939556</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4507,10 +4520,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467821</v>
+        <v>467815</v>
       </c>
       <c r="R38" t="n">
-        <v>6875508</v>
+        <v>6875541</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4568,13 +4581,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104939568</t>
+          <t>https://artportalen.se/Sighting/104939556</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104939578</v>
+        <v>104939568</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4610,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467788</v>
+        <v>467821</v>
       </c>
       <c r="R39" t="n">
-        <v>6875461</v>
+        <v>6875508</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4671,13 +4684,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104939578</t>
+          <t>https://artportalen.se/Sighting/104939568</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111527806</v>
+        <v>104939578</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4709,17 +4722,17 @@
       <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467615</v>
+        <v>467788</v>
       </c>
       <c r="R40" t="n">
-        <v>6875427</v>
+        <v>6875461</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4743,12 +4756,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4774,13 +4787,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111527806</t>
+          <t>https://artportalen.se/Sighting/104939578</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111528203</v>
+        <v>111527806</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -4812,14 +4825,14 @@
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467745</v>
+        <v>467615</v>
       </c>
       <c r="R41" t="n">
-        <v>6875430</v>
+        <v>6875427</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4877,13 +4890,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111528203</t>
+          <t>https://artportalen.se/Sighting/111527806</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111528300</v>
+        <v>111528203</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -4919,10 +4932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467795</v>
+        <v>467745</v>
       </c>
       <c r="R42" t="n">
-        <v>6875452</v>
+        <v>6875430</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4957,11 +4970,6 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Tre blommande.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4985,13 +4993,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111528300</t>
+          <t>https://artportalen.se/Sighting/111528203</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111528980</v>
+        <v>111528300</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5027,10 +5035,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467800</v>
+        <v>467795</v>
       </c>
       <c r="R43" t="n">
-        <v>6875540</v>
+        <v>6875452</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5065,6 +5073,11 @@
           <t>2023-08-17</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tre blommande.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5088,13 +5101,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111528980</t>
+          <t>https://artportalen.se/Sighting/111528300</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111908768</v>
+        <v>111528980</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5122,11 +5135,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5134,10 +5143,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467912</v>
+        <v>467800</v>
       </c>
       <c r="R44" t="n">
-        <v>6875300</v>
+        <v>6875540</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5164,12 +5173,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5195,13 +5204,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111908768</t>
+          <t>https://artportalen.se/Sighting/111528980</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118153320</v>
+        <v>111908768</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5231,24 +5240,20 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467531</v>
+        <v>467912</v>
       </c>
       <c r="R45" t="n">
-        <v>6875351</v>
+        <v>6875300</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5275,17 +5280,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tre stycken som är i förstadium till blomning.</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5311,13 +5311,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153320</t>
+          <t>https://artportalen.se/Sighting/111908768</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118153438</v>
+        <v>118153320</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5361,13 +5361,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467534</v>
+        <v>467531</v>
       </c>
       <c r="R46" t="n">
-        <v>6875341</v>
+        <v>6875351</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En blomknopp.</t>
+          <t>Tre stycken som är i förstadium till blomning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5427,13 +5427,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153438</t>
+          <t>https://artportalen.se/Sighting/118153320</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118153540</v>
+        <v>118153438</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467572</v>
+        <v>467534</v>
       </c>
       <c r="R47" t="n">
-        <v>6875307</v>
+        <v>6875341</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Två blomknopp.</t>
+          <t>En blomknopp.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5543,13 +5543,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153540</t>
+          <t>https://artportalen.se/Sighting/118153438</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118587202</v>
+        <v>118153540</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5587,24 +5587,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467585</v>
+        <v>467572</v>
       </c>
       <c r="R48" t="n">
-        <v>6875479</v>
+        <v>6875307</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5628,12 +5623,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Två blomknopp.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,13 +5659,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587202</t>
+          <t>https://artportalen.se/Sighting/118153540</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118587288</v>
+        <v>118587202</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5703,19 +5703,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467579</v>
+        <v>467585</v>
       </c>
       <c r="R49" t="n">
-        <v>6875483</v>
+        <v>6875479</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5745,11 +5750,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>En blomma.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5775,13 +5775,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587288</t>
+          <t>https://artportalen.se/Sighting/118587202</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118587643</v>
+        <v>118587288</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5825,13 +5825,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467611</v>
+        <v>467579</v>
       </c>
       <c r="R50" t="n">
-        <v>6875400</v>
+        <v>6875483</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Fyra blommande exemplar.</t>
+          <t>En blomma.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5891,13 +5891,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587643</t>
+          <t>https://artportalen.se/Sighting/118587288</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118587687</v>
+        <v>118587643</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467571</v>
+        <v>467611</v>
       </c>
       <c r="R51" t="n">
-        <v>6875367</v>
+        <v>6875400</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Fem blommande exemplar.</t>
+          <t>Fyra blommande exemplar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6007,13 +6007,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587687</t>
+          <t>https://artportalen.se/Sighting/118587643</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118587849</v>
+        <v>118587687</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467399</v>
+        <v>467571</v>
       </c>
       <c r="R52" t="n">
         <v>6875367</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ett blommande exemplar.</t>
+          <t>Fem blommande exemplar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6123,13 +6123,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587849</t>
+          <t>https://artportalen.se/Sighting/118587687</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120101759</v>
+        <v>118587849</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6169,17 +6169,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467781</v>
+        <v>467399</v>
       </c>
       <c r="R53" t="n">
-        <v>6875230</v>
+        <v>6875367</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6203,17 +6203,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I avverkningsanmälan.</t>
+          <t>Ett blommande exemplar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,13 +6239,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101759</t>
+          <t>https://artportalen.se/Sighting/118587849</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120177573</v>
+        <v>120101759</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467874</v>
+        <v>467781</v>
       </c>
       <c r="R54" t="n">
-        <v>6875439</v>
+        <v>6875230</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6319,17 +6319,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
+          <t>I avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6355,13 +6355,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120177573</t>
+          <t>https://artportalen.se/Sighting/120101759</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127037135</v>
+        <v>120177573</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6399,24 +6399,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467944</v>
+        <v>467874</v>
       </c>
       <c r="R55" t="n">
-        <v>6875455</v>
+        <v>6875439</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6440,12 +6435,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6471,56 +6471,68 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127037135</t>
+          <t>https://artportalen.se/Sighting/120177573</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101933379</v>
+        <v>127037135</v>
       </c>
       <c r="B56" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467433</v>
+        <v>467944</v>
       </c>
       <c r="R56" t="n">
-        <v>6875384</v>
+        <v>6875455</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6544,12 +6556,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6575,13 +6587,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933379</t>
+          <t>https://artportalen.se/Sighting/127037135</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118587106</v>
+        <v>101933379</v>
       </c>
       <c r="B57" t="n">
         <v>97989</v>
@@ -6610,19 +6622,21 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467580</v>
+        <v>467433</v>
       </c>
       <c r="R57" t="n">
-        <v>6875466</v>
+        <v>6875384</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6646,17 +6660,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Oräkneligt antal, fler än 300.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6682,16 +6691,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587106</t>
+          <t>https://artportalen.se/Sighting/101933379</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118153108</v>
+        <v>118587106</v>
       </c>
       <c r="B58" t="n">
-        <v>99140</v>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6699,21 +6708,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6723,10 +6732,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467495</v>
+        <v>467580</v>
       </c>
       <c r="R58" t="n">
-        <v>6875373</v>
+        <v>6875466</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6753,12 +6762,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Oräkneligt antal, fler än 300.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6784,52 +6798,51 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153108</t>
+          <t>https://artportalen.se/Sighting/118587106</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111942915</v>
+        <v>118153108</v>
       </c>
       <c r="B59" t="n">
-        <v>79917</v>
+        <v>99140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468248</v>
+        <v>467495</v>
       </c>
       <c r="R59" t="n">
-        <v>6875167</v>
+        <v>6875373</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6856,12 +6869,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6887,16 +6900,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111942915</t>
+          <t>https://artportalen.se/Sighting/118153108</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111942872</v>
+        <v>111942915</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6904,21 +6917,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6929,10 +6942,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468260</v>
+        <v>468248</v>
       </c>
       <c r="R60" t="n">
-        <v>6875164</v>
+        <v>6875167</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6989,6 +7002,225 @@
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942915</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135808905</v>
+      </c>
+      <c r="B61" t="n">
+        <v>93357</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>468257</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6874713</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135808905</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>111942872</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>468260</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6875164</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111942872</t>
         </is>
@@ -7055,6 +7287,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>135808905</v>
       </c>
       <c r="B61" t="n">
-        <v>93357</v>
+        <v>93359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>135808905</v>
       </c>
       <c r="B61" t="n">
-        <v>93359</v>
+        <v>93374</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>135808905</v>
       </c>
       <c r="B61" t="n">
-        <v>93374</v>
+        <v>93375</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>135808905</v>
       </c>
       <c r="B61" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120182061</v>
+        <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,37 +1013,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467868</v>
+        <v>468204</v>
       </c>
       <c r="R5" t="n">
-        <v>6875214</v>
+        <v>6874631</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,61 +1112,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120182061</t>
+          <t>https://artportalen.se/Sighting/136277264</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111908700</v>
+        <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>92509</v>
+        <v>93377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467922</v>
+        <v>468228</v>
       </c>
       <c r="R6" t="n">
-        <v>6875306</v>
+        <v>6874650</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1179,17 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Förekomst av doftticka i avverkningsanmält område.</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,52 +1214,60 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111908700</t>
+          <t>https://artportalen.se/Sighting/136277249</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111942953</v>
+        <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>93009</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Sveg, Hjd, Fläcksberget, Sveg, Hjd, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468248</v>
+        <v>468038</v>
       </c>
       <c r="R7" t="n">
-        <v>6875167</v>
+        <v>6874871</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,12 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,55 +1325,68 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111942953</t>
+          <t>https://artportalen.se/Sighting/136271964</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112014229</v>
+        <v>136272648</v>
       </c>
       <c r="B8" t="n">
-        <v>93213</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467427</v>
+        <v>468049</v>
       </c>
       <c r="R8" t="n">
-        <v>6875290</v>
+        <v>6874874</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,12 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,52 +1441,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014229</t>
+          <t>https://artportalen.se/Sighting/136272648</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111909766</v>
+        <v>136272215</v>
       </c>
       <c r="B9" t="n">
-        <v>91680</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467757</v>
+        <v>468075</v>
       </c>
       <c r="R9" t="n">
-        <v>6875470</v>
+        <v>6874873</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1493,12 +1512,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,16 +1548,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909766</t>
+          <t>https://artportalen.se/Sighting/136272215</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112014208</v>
+        <v>136272621</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,35 +1565,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467418</v>
+        <v>468069</v>
       </c>
       <c r="R10" t="n">
-        <v>6875312</v>
+        <v>6874862</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1596,12 +1619,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,16 +1655,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014208</t>
+          <t>https://artportalen.se/Sighting/136272621</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112014423</v>
+        <v>120182061</v>
       </c>
       <c r="B11" t="n">
-        <v>93189</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,38 +1672,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467430</v>
+        <v>467868</v>
       </c>
       <c r="R11" t="n">
-        <v>6875238</v>
+        <v>6875214</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,12 +1726,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,16 +1757,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014423</t>
+          <t>https://artportalen.se/Sighting/120182061</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112014834</v>
+        <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>93189</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,35 +1774,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467492</v>
+        <v>468059</v>
       </c>
       <c r="R12" t="n">
-        <v>6875044</v>
+        <v>6875258</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1802,12 +1828,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1833,52 +1859,61 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014834</t>
+          <t>https://artportalen.se/Sighting/136276411</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112015011</v>
+        <v>111908700</v>
       </c>
       <c r="B13" t="n">
-        <v>93189</v>
+        <v>92509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467390</v>
+        <v>467922</v>
       </c>
       <c r="R13" t="n">
-        <v>6875328</v>
+        <v>6875306</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1905,12 +1940,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Förekomst av doftticka i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,55 +1976,55 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112015011</t>
+          <t>https://artportalen.se/Sighting/111908700</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105096262</v>
+        <v>111942953</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fläcksberget, Sveg, Hjd, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467919</v>
+        <v>468248</v>
       </c>
       <c r="R14" t="n">
-        <v>6875084</v>
+        <v>6875167</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2008,12 +2048,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,38 +2079,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105096262</t>
+          <t>https://artportalen.se/Sighting/111942953</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112014142</v>
+        <v>112014229</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467443</v>
+        <v>467427</v>
       </c>
       <c r="R15" t="n">
-        <v>6875337</v>
+        <v>6875290</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2142,51 +2182,52 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014142</t>
+          <t>https://artportalen.se/Sighting/112014229</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706366</v>
+        <v>111909766</v>
       </c>
       <c r="B16" t="n">
-        <v>93197</v>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467673</v>
+        <v>467757</v>
       </c>
       <c r="R16" t="n">
-        <v>6875271</v>
+        <v>6875470</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2213,22 +2254,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,27 +2274,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119706366</t>
+          <t>https://artportalen.se/Sighting/111909766</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120176783</v>
+        <v>112014208</v>
       </c>
       <c r="B17" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,43 +2302,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467915</v>
+        <v>467418</v>
       </c>
       <c r="R17" t="n">
-        <v>6875340</v>
+        <v>6875312</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2334,12 +2357,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,16 +2388,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120176783</t>
+          <t>https://artportalen.se/Sighting/112014208</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120178153</v>
+        <v>112014423</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,34 +2405,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467623</v>
+        <v>467430</v>
       </c>
       <c r="R18" t="n">
-        <v>6875374</v>
+        <v>6875238</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2436,12 +2460,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2467,16 +2491,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120178153</t>
+          <t>https://artportalen.se/Sighting/112014423</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112014347</v>
+        <v>112014834</v>
       </c>
       <c r="B19" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467430</v>
+        <v>467492</v>
       </c>
       <c r="R19" t="n">
-        <v>6875238</v>
+        <v>6875044</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2570,16 +2594,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014347</t>
+          <t>https://artportalen.se/Sighting/112014834</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112014177</v>
+        <v>112015011</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,21 +2611,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2673,16 +2697,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014177</t>
+          <t>https://artportalen.se/Sighting/112015011</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112014300</v>
+        <v>105096262</v>
       </c>
       <c r="B21" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,38 +2714,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Sveg, Hjd, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467415</v>
+        <v>467919</v>
       </c>
       <c r="R21" t="n">
-        <v>6875288</v>
+        <v>6875084</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2745,12 +2769,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,16 +2800,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014300</t>
+          <t>https://artportalen.se/Sighting/105096262</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112014923</v>
+        <v>112014142</v>
       </c>
       <c r="B22" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,21 +2817,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2818,10 +2842,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467413</v>
+        <v>467443</v>
       </c>
       <c r="R22" t="n">
-        <v>6875235</v>
+        <v>6875337</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2879,16 +2903,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112014923</t>
+          <t>https://artportalen.se/Sighting/112014142</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111909174</v>
+        <v>119706366</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,35 +2920,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467989</v>
+        <v>467673</v>
       </c>
       <c r="R23" t="n">
-        <v>6875352</v>
+        <v>6875271</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2951,12 +2974,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2971,27 +3004,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909174</t>
+          <t>https://artportalen.se/Sighting/119706366</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111909536</v>
+        <v>120176783</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,35 +3032,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467891</v>
+        <v>467915</v>
       </c>
       <c r="R24" t="n">
-        <v>6875425</v>
+        <v>6875340</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3054,12 +3095,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3085,16 +3126,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909536</t>
+          <t>https://artportalen.se/Sighting/120176783</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111942712</v>
+        <v>120178153</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,35 +3143,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468231</v>
+        <v>467623</v>
       </c>
       <c r="R25" t="n">
-        <v>6875022</v>
+        <v>6875374</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3157,12 +3197,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,16 +3228,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111942712</t>
+          <t>https://artportalen.se/Sighting/120178153</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176592</v>
+        <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,34 +3245,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467835</v>
+        <v>468241</v>
       </c>
       <c r="R26" t="n">
-        <v>6875180</v>
+        <v>6875168</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3259,12 +3308,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,16 +3339,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120176592</t>
+          <t>https://artportalen.se/Sighting/136276717</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120178856</v>
+        <v>112014347</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3307,34 +3356,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467636</v>
+        <v>467430</v>
       </c>
       <c r="R27" t="n">
-        <v>6875381</v>
+        <v>6875238</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3361,12 +3411,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3392,16 +3442,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120178856</t>
+          <t>https://artportalen.se/Sighting/112014347</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119705999</v>
+        <v>112014177</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3409,48 +3459,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467790</v>
+        <v>467390</v>
       </c>
       <c r="R28" t="n">
-        <v>6875238</v>
+        <v>6875328</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3477,22 +3514,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3507,81 +3534,63 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119705999</t>
+          <t>https://artportalen.se/Sighting/112014177</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120101688</v>
+        <v>112014300</v>
       </c>
       <c r="B29" t="n">
-        <v>57141</v>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467781</v>
+        <v>467415</v>
       </c>
       <c r="R29" t="n">
-        <v>6875230</v>
+        <v>6875288</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3608,12 +3617,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,60 +3648,52 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101688</t>
+          <t>https://artportalen.se/Sighting/112014300</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120178180</v>
+        <v>112014923</v>
       </c>
       <c r="B30" t="n">
-        <v>57141</v>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467592</v>
+        <v>467413</v>
       </c>
       <c r="R30" t="n">
-        <v>6875379</v>
+        <v>6875235</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3719,12 +3720,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3750,56 +3751,55 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120178180</t>
+          <t>https://artportalen.se/Sighting/112014923</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101933361</v>
+        <v>111909174</v>
       </c>
       <c r="B31" t="n">
-        <v>99022</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220093</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467341</v>
+        <v>467989</v>
       </c>
       <c r="R31" t="n">
-        <v>6875408</v>
+        <v>6875352</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3854,56 +3854,55 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933361</t>
+          <t>https://artportalen.se/Sighting/111909174</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101933401</v>
+        <v>111909536</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467487</v>
+        <v>467891</v>
       </c>
       <c r="R32" t="n">
-        <v>6875372</v>
+        <v>6875425</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3927,12 +3926,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3958,56 +3957,55 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933401</t>
+          <t>https://artportalen.se/Sighting/111909536</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101933424</v>
+        <v>111942712</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467573</v>
+        <v>468231</v>
       </c>
       <c r="R33" t="n">
-        <v>6875315</v>
+        <v>6875022</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4031,12 +4029,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,56 +4060,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933424</t>
+          <t>https://artportalen.se/Sighting/111942712</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101933453</v>
+        <v>120176592</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467584</v>
+        <v>467835</v>
       </c>
       <c r="R34" t="n">
-        <v>6875343</v>
+        <v>6875180</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4135,12 +4131,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,56 +4162,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933453</t>
+          <t>https://artportalen.se/Sighting/120176592</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101933471</v>
+        <v>120178856</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467562</v>
+        <v>467636</v>
       </c>
       <c r="R35" t="n">
-        <v>6875360</v>
+        <v>6875381</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4239,12 +4233,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4270,56 +4264,68 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933471</t>
+          <t>https://artportalen.se/Sighting/120178856</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101933482</v>
+        <v>119705999</v>
       </c>
       <c r="B36" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467592</v>
+        <v>467790</v>
       </c>
       <c r="R36" t="n">
-        <v>6875418</v>
+        <v>6875238</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4343,12 +4349,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,64 +4379,62 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933482</t>
+          <t>https://artportalen.se/Sighting/119705999</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101933494</v>
+        <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>99118</v>
+        <v>80064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467614</v>
+        <v>468192</v>
       </c>
       <c r="R37" t="n">
-        <v>6875407</v>
+        <v>6875098</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4447,12 +4461,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4478,55 +4492,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933494</t>
+          <t>https://artportalen.se/Sighting/136275098</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104939556</v>
+        <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>80064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467815</v>
+        <v>468172</v>
       </c>
       <c r="R38" t="n">
-        <v>6875541</v>
+        <v>6875102</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4550,12 +4563,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4581,55 +4594,54 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104939556</t>
+          <t>https://artportalen.se/Sighting/136275148</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104939568</v>
+        <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>99118</v>
+        <v>78449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467821</v>
+        <v>468175</v>
       </c>
       <c r="R39" t="n">
-        <v>6875508</v>
+        <v>6875128</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4653,12 +4665,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,55 +4696,54 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104939568</t>
+          <t>https://artportalen.se/Sighting/136275244</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104939578</v>
+        <v>136275528</v>
       </c>
       <c r="B40" t="n">
-        <v>99118</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467788</v>
+        <v>468083</v>
       </c>
       <c r="R40" t="n">
-        <v>6875461</v>
+        <v>6875192</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4756,12 +4767,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4787,52 +4803,70 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104939578</t>
+          <t>https://artportalen.se/Sighting/136275528</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111527806</v>
+        <v>120101688</v>
       </c>
       <c r="B41" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467615</v>
+        <v>467781</v>
       </c>
       <c r="R41" t="n">
-        <v>6875427</v>
+        <v>6875230</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4859,12 +4893,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,52 +4924,60 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111527806</t>
+          <t>https://artportalen.se/Sighting/120101688</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111528203</v>
+        <v>120178180</v>
       </c>
       <c r="B42" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467745</v>
+        <v>467592</v>
       </c>
       <c r="R42" t="n">
-        <v>6875430</v>
+        <v>6875379</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4962,12 +5004,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4993,55 +5035,56 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111528203</t>
+          <t>https://artportalen.se/Sighting/120178180</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111528300</v>
+        <v>101933361</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467795</v>
+        <v>467341</v>
       </c>
       <c r="R43" t="n">
-        <v>6875452</v>
+        <v>6875408</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5065,17 +5108,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tre blommande.</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5101,13 +5139,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111528300</t>
+          <t>https://artportalen.se/Sighting/101933361</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111528980</v>
+        <v>101933401</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5137,19 +5175,20 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467800</v>
+        <v>467487</v>
       </c>
       <c r="R44" t="n">
-        <v>6875540</v>
+        <v>6875372</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5173,12 +5212,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5204,13 +5243,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111528980</t>
+          <t>https://artportalen.se/Sighting/101933401</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111908768</v>
+        <v>101933424</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5238,25 +5277,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467912</v>
+        <v>467573</v>
       </c>
       <c r="R45" t="n">
-        <v>6875300</v>
+        <v>6875315</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5280,12 +5316,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5311,13 +5347,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111908768</t>
+          <t>https://artportalen.se/Sighting/101933424</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118153320</v>
+        <v>101933453</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5345,29 +5381,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467531</v>
+        <v>467584</v>
       </c>
       <c r="R46" t="n">
-        <v>6875351</v>
+        <v>6875343</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5391,17 +5420,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Tre stycken som är i förstadium till blomning.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5427,13 +5451,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153320</t>
+          <t>https://artportalen.se/Sighting/101933453</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118153438</v>
+        <v>101933471</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5461,29 +5485,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467534</v>
+        <v>467562</v>
       </c>
       <c r="R47" t="n">
-        <v>6875341</v>
+        <v>6875360</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5507,17 +5524,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En blomknopp.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5543,13 +5555,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153438</t>
+          <t>https://artportalen.se/Sighting/101933471</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118153540</v>
+        <v>101933482</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5577,29 +5589,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467572</v>
+        <v>467592</v>
       </c>
       <c r="R48" t="n">
-        <v>6875307</v>
+        <v>6875418</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5623,17 +5628,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Två blomknopp.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,13 +5659,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153540</t>
+          <t>https://artportalen.se/Sighting/101933482</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118587202</v>
+        <v>101933494</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5693,34 +5693,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467585</v>
+        <v>467614</v>
       </c>
       <c r="R49" t="n">
-        <v>6875479</v>
+        <v>6875407</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5744,12 +5732,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5775,13 +5763,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587202</t>
+          <t>https://artportalen.se/Sighting/101933494</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118587288</v>
+        <v>104939556</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5809,29 +5797,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467579</v>
+        <v>467815</v>
       </c>
       <c r="R50" t="n">
-        <v>6875483</v>
+        <v>6875541</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5855,17 +5835,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>En blomma.</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5891,13 +5866,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587288</t>
+          <t>https://artportalen.se/Sighting/104939556</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118587643</v>
+        <v>104939568</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5925,29 +5900,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467611</v>
+        <v>467821</v>
       </c>
       <c r="R51" t="n">
-        <v>6875400</v>
+        <v>6875508</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5971,17 +5938,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fyra blommande exemplar.</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6007,13 +5969,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587643</t>
+          <t>https://artportalen.se/Sighting/104939568</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118587687</v>
+        <v>104939578</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6041,29 +6003,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467571</v>
+        <v>467788</v>
       </c>
       <c r="R52" t="n">
-        <v>6875367</v>
+        <v>6875461</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6087,17 +6041,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fem blommande exemplar.</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6123,13 +6072,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587687</t>
+          <t>https://artportalen.se/Sighting/104939578</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118587849</v>
+        <v>111527806</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6157,29 +6106,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+          <t>Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467399</v>
+        <v>467615</v>
       </c>
       <c r="R53" t="n">
-        <v>6875367</v>
+        <v>6875427</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6203,17 +6144,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ett blommande exemplar.</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,13 +6175,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587849</t>
+          <t>https://artportalen.se/Sighting/111527806</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120101759</v>
+        <v>111528203</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6273,26 +6209,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467781</v>
+        <v>467745</v>
       </c>
       <c r="R54" t="n">
-        <v>6875230</v>
+        <v>6875430</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6319,17 +6247,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälan.</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6355,13 +6278,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120101759</t>
+          <t>https://artportalen.se/Sighting/111528203</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120177573</v>
+        <v>111528300</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6389,26 +6312,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467874</v>
+        <v>467795</v>
       </c>
       <c r="R55" t="n">
-        <v>6875439</v>
+        <v>6875452</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6435,17 +6350,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
+          <t>Tre blommande.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6471,13 +6386,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120177573</t>
+          <t>https://artportalen.se/Sighting/111528300</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127037135</v>
+        <v>111528980</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6505,34 +6420,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467944</v>
+        <v>467800</v>
       </c>
       <c r="R56" t="n">
-        <v>6875455</v>
+        <v>6875540</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6556,12 +6458,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6587,56 +6489,59 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127037135</t>
+          <t>https://artportalen.se/Sighting/111528980</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101933379</v>
+        <v>111908768</v>
       </c>
       <c r="B57" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fläcksberget V, Hjd</t>
+          <t>Fläcksberget, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467433</v>
+        <v>467912</v>
       </c>
       <c r="R57" t="n">
-        <v>6875384</v>
+        <v>6875300</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6660,12 +6565,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,51 +6596,60 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101933379</t>
+          <t>https://artportalen.se/Sighting/111908768</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118587106</v>
+        <v>118153320</v>
       </c>
       <c r="B58" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467580</v>
+        <v>467531</v>
       </c>
       <c r="R58" t="n">
-        <v>6875466</v>
+        <v>6875351</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6762,17 +6676,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Oräkneligt antal, fler än 300.</t>
+          <t>Tre stycken som är i förstadium till blomning.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6798,54 +6712,63 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118587106</t>
+          <t>https://artportalen.se/Sighting/118153320</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118153108</v>
+        <v>118153438</v>
       </c>
       <c r="B59" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467495</v>
+        <v>467534</v>
       </c>
       <c r="R59" t="n">
-        <v>6875373</v>
+        <v>6875341</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6875,6 +6798,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>En blomknopp.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6900,52 +6828,60 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118153108</t>
+          <t>https://artportalen.se/Sighting/118153438</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111942915</v>
+        <v>118153540</v>
       </c>
       <c r="B60" t="n">
-        <v>79917</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468248</v>
+        <v>467572</v>
       </c>
       <c r="R60" t="n">
-        <v>6875167</v>
+        <v>6875307</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6972,12 +6908,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Två blomknopp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,38 +6944,38 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111942915</t>
+          <t>https://artportalen.se/Sighting/118153540</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135808905</v>
+        <v>118587202</v>
       </c>
       <c r="B61" t="n">
-        <v>93376</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7044,27 +6985,27 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fläcksberget, Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468257</v>
+        <v>467585</v>
       </c>
       <c r="R61" t="n">
-        <v>6874713</v>
+        <v>6875479</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7088,12 +7029,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7119,52 +7060,60 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135808905</t>
+          <t>https://artportalen.se/Sighting/118587202</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>111942872</v>
+        <v>118587288</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fläcksberget, Hjd</t>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468260</v>
+        <v>467579</v>
       </c>
       <c r="R62" t="n">
-        <v>6875164</v>
+        <v>6875483</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7191,12 +7140,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>En blomma.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7221,6 +7175,1902 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587288</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>118587643</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>467611</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6875400</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fyra blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587643</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>118587687</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>467571</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6875367</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fem blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587687</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>118587849</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>467399</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6875367</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ett blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587849</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120101759</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>467781</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6875230</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101759</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120177573</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>467874</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6875439</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Cirka 80 rosetter inom 6x2 meter i avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120177573</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127037135</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>467944</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6875455</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127037135</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>101933379</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>467433</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6875384</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933379</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>118587106</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>467580</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6875466</v>
+      </c>
+      <c r="S70" t="n">
+        <v>20</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Oräkneligt antal, fler än 300.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587106</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>118153108</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fläcksberget V, Fläcksberget V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>467495</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6875373</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118153108</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>111942915</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>468248</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6875167</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942915</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136277068</v>
+      </c>
+      <c r="B73" t="n">
+        <v>93365</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>468465</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6874919</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136277068</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135808905</v>
+      </c>
+      <c r="B74" t="n">
+        <v>93377</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>468257</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6874713</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135808905</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136277183</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93377</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>468263</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6874720</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136277183</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136277198</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93377</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>468257</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6874715</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136277198</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136276878</v>
+      </c>
+      <c r="B77" t="n">
+        <v>93365</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>468329</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6875120</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136276878</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136276940</v>
+      </c>
+      <c r="B78" t="n">
+        <v>93365</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>468364</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6875106</v>
+      </c>
+      <c r="S78" t="n">
+        <v>20</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136276940</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>111942872</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>468260</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6875164</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111942872</t>
         </is>
@@ -7289,6 +9139,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93009</v>
+        <v>93015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136272648</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136272215</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136272621</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136275528</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135808905</v>
       </c>
       <c r="B74" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136272648</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136272215</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136272621</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136275528</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135808905</v>
       </c>
       <c r="B74" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93384</v>
+        <v>93390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93016</v>
+        <v>93022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135808905</v>
       </c>
       <c r="B74" t="n">
-        <v>93384</v>
+        <v>93390</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93384</v>
+        <v>93390</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93384</v>
+        <v>93390</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93390</v>
+        <v>93397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136272648</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136272215</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136272621</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136275528</v>
       </c>
       <c r="B40" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135808905</v>
       </c>
       <c r="B74" t="n">
-        <v>93390</v>
+        <v>93397</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93390</v>
+        <v>93397</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93390</v>
+        <v>93397</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93029</v>
+        <v>93030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135808905</v>
       </c>
       <c r="B74" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>135808070</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93030</v>
+        <v>93043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136272648</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136272215</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136272621</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136275528</v>
       </c>
       <c r="B40" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135808905</v>
       </c>
       <c r="B74" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93043</v>
+        <v>93044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
